--- a/docs/ValueSet-ahip-religion-christian-detail.xlsx
+++ b/docs/ValueSet-ahip-religion-christian-detail.xlsx
@@ -49,7 +49,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>AHIP Christian Religion Detail Codes</t>
+    <t>Used as the answer options for the Christian denomination detail question, shown only when the patient selects Christian on the religion/spirituality question.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -208,7 +208,7 @@
     <t>Orthodox Russian</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-religion-codes</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-religion-codes</t>
   </si>
 </sst>
 </file>

--- a/docs/ValueSet-ahip-religion-christian-detail.xlsx
+++ b/docs/ValueSet-ahip-religion-christian-detail.xlsx
@@ -94,7 +94,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -124,91 +125,91 @@
     <t>Calvinist/Reformed</t>
   </si>
   <si>
-    <t>1068</t>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>Episcopalian</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>Lutheran</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>Methodist</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>Nondenominational</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>Pentecostal</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>Presbyterian</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>Roman Catholic</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>Seventh-day Adventist</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>Orthodox Christian</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ReligiousAffiliation</t>
+  </si>
+  <si>
+    <t>ORCO</t>
+  </si>
+  <si>
+    <t>Coptic Orthodox</t>
+  </si>
+  <si>
+    <t>CAEA</t>
   </si>
   <si>
     <t>Eastern Catholic</t>
   </si>
   <si>
-    <t>1069</t>
-  </si>
-  <si>
-    <t>Episcopalian</t>
-  </si>
-  <si>
-    <t>1028</t>
-  </si>
-  <si>
-    <t>Lutheran</t>
-  </si>
-  <si>
-    <t>1073</t>
-  </si>
-  <si>
-    <t>Methodist</t>
-  </si>
-  <si>
-    <t>1078</t>
-  </si>
-  <si>
-    <t>Nondenominational</t>
-  </si>
-  <si>
-    <t>1038</t>
-  </si>
-  <si>
-    <t>Pentecostal</t>
-  </si>
-  <si>
-    <t>1040</t>
-  </si>
-  <si>
-    <t>Presbyterian</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>Roman Catholic</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>Seventh-day Adventist</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>Orthodox Christian</t>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-ReligiousAffiliation</t>
-  </si>
-  <si>
-    <t>ORCO</t>
-  </si>
-  <si>
-    <t>Orthodox Coptic</t>
-  </si>
-  <si>
     <t>ORGR</t>
   </si>
   <si>
-    <t>Orthodox Greek</t>
+    <t>Greek Orthodox Church</t>
   </si>
   <si>
     <t>ORRU</t>
   </si>
   <si>
-    <t>Orthodox Russian</t>
-  </si>
-  <si>
-    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-religion-codes</t>
+    <t>Russian Orthodox Church</t>
+  </si>
+  <si>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-temporary-codes</t>
   </si>
 </sst>
 </file>
@@ -474,7 +475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -587,26 +588,18 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -616,7 +609,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -633,41 +626,49 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>64</v>
       </c>
     </row>
